--- a/SFN/covariates/Trust Full Covariates.xlsx
+++ b/SFN/covariates/Trust Full Covariates.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/avidachs/Documents/GitHub/rf1-sra-trust/SFN/covariates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{356F70BC-0B3B-8448-85D0-7C9CBD9D0D9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8F619BC-2B3A-2141-BC97-13608675328D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16120" xr2:uid="{4E11F570-9D62-564C-8056-C5AD2FBE54C5}"/>
   </bookViews>
